--- a/deals_data.xlsx
+++ b/deals_data.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\OneDrive\Desktop\Padmavathi\Sareedeals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3597E47C-DB45-40F9-92F1-44690464609C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA7984F-C591-4245-9048-E2FDE0AA2506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5486" yWindow="3540" windowWidth="16457" windowHeight="9454" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Deals" sheetId="1" r:id="rId1"/>
+    <sheet name="Home" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -119,13 +120,46 @@
   </si>
   <si>
     <t>Premium soft georgette saree featuring a smooth finish and lightweight drape, designed to enhance elegance with effortless comfort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanderi Cotton </t>
+  </si>
+  <si>
+    <t>Elegant, traditional handwoven textile from Madhya Pradesh. Renowned for its lightweight, translucent quality—often referred to as "woven air"—it combines breathable cotton comfort with a subtle, regal gloss and delicate metallic detailing</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dq6jpmn1z/image/upload/v1780994824/sr2_bas77v.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dq6jpmn1z/image/upload/v1780994823/sr1_vpnbij.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dq6jpmn1z/image/upload/v1780994823/sr3_xagcwv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dq6jpmn1z/image/upload/v1780994823/sr6_fhp0d0.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dq6jpmn1z/image/upload/v1780994823/sr5_dsa21g.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dq6jpmn1z/image/upload/v1780994822/sr8_lpq4oj.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dq6jpmn1z/image/upload/v1780994823/sr4_ewmipe.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dq6jpmn1z/image/upload/v1780994823/sr7_psmese.jpg</t>
+  </si>
+  <si>
+    <t>Fancy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +176,14 @@
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -202,10 +244,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -240,8 +283,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -910,4 +955,307 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB8B6E95-EDF6-4F99-82F6-389E21F21DD5}">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="14.921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.69140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.07421875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.4609375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.07421875" customWidth="1"/>
+    <col min="9" max="9" width="66.69140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="130.84375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1150</v>
+      </c>
+      <c r="E2" s="2">
+        <v>399</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1150</v>
+      </c>
+      <c r="E3" s="2">
+        <v>399</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1150</v>
+      </c>
+      <c r="E4" s="2">
+        <v>399</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1150</v>
+      </c>
+      <c r="E5" s="2">
+        <v>399</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1150</v>
+      </c>
+      <c r="E6" s="2">
+        <v>399</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1150</v>
+      </c>
+      <c r="E7" s="2">
+        <v>399</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1150</v>
+      </c>
+      <c r="E8" s="2">
+        <v>399</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1150</v>
+      </c>
+      <c r="E9" s="2">
+        <v>399</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{84D57247-1F3D-4556-904A-0BD389FF0EAD}"/>
+    <hyperlink ref="H4" r:id="rId2" xr:uid="{24E4645B-D6DE-437C-806C-9D77F0CF3DAF}"/>
+    <hyperlink ref="H5" r:id="rId3" xr:uid="{99A88F89-A9BB-4740-85F3-7B633B5EDC62}"/>
+    <hyperlink ref="H6" r:id="rId4" xr:uid="{45FBA0A1-926C-4AD0-BA34-C1806025F34E}"/>
+    <hyperlink ref="H7" r:id="rId5" xr:uid="{1ED11340-52FE-4C52-A78F-77CFC43CFE07}"/>
+    <hyperlink ref="H8" r:id="rId6" xr:uid="{B5A0B35D-5FC6-4B47-A00E-33AB8B99CBC1}"/>
+    <hyperlink ref="H9" r:id="rId7" xr:uid="{8E6E5AC2-3187-4383-B368-D078A00E93B8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>